--- a/data/macro/South Korea/South Korea Export.xlsx
+++ b/data/macro/South Korea/South Korea Export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AA0A8C-4EA8-4BA2-917D-97CF634EACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE3A9A7-4FFD-4E88-83F7-DA7FF0BAD356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0939876-3207-4808-9706-D07754E61412}"/>
   </bookViews>
@@ -18001,6 +18001,15 @@
       <c r="D788" s="7" t="s">
         <v>6</v>
       </c>
+      <c r="E788" s="12">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="F788" s="12">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="G788" s="12">
+        <v>0.28699999999999998</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G781">

--- a/data/macro/South Korea/South Korea Export.xlsx
+++ b/data/macro/South Korea/South Korea Export.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE3A9A7-4FFD-4E88-83F7-DA7FF0BAD356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76664FC-C6C3-4749-A8B5-9F89D980AB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0939876-3207-4808-9706-D07754E61412}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="13">
   <si>
     <t>Release Date</t>
   </si>
@@ -535,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E811BE6-6834-4321-8CFC-3896E109A5F4}">
-  <dimension ref="A1:J788"/>
+  <dimension ref="A1:J790"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
@@ -18009,6 +18009,52 @@
       </c>
       <c r="G788" s="12">
         <v>0.28699999999999998</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A789" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B789" s="6">
+        <v>46143</v>
+      </c>
+      <c r="C789" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="D789" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E789" s="12">
+        <v>0.48</v>
+      </c>
+      <c r="F789" s="12">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="G789" s="12">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="H789" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A790" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B790" s="6">
+        <v>46157</v>
+      </c>
+      <c r="C790" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="D790" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F790" s="12">
+        <v>0.48</v>
+      </c>
+      <c r="G790" s="12">
+        <v>0.49199999999999999</v>
       </c>
     </row>
   </sheetData>
